--- a/jpcore-r4/feature/fix-tx-error/StructureDefinition-jp-imagingstudy-endoscopy.xlsx
+++ b/jpcore-r4/feature/fix-tx-error/StructureDefinition-jp-imagingstudy-endoscopy.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2146" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2147" uniqueCount="454">
   <si>
     <t>Property</t>
   </si>
@@ -852,7 +852,10 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>http://playbook.radlex.org/playbook/SearchRadlexAction</t>
+    <t>実行された手順のタイプ。</t>
+  </si>
+  <si>
+    <t>http://www.rsna.org/RadLex_Playbook.aspx</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -4553,9 +4556,11 @@
       <c r="X24" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="Y24" s="2"/>
+      <c r="Y24" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="Z24" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>79</v>
@@ -4588,7 +4593,7 @@
         <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>258</v>
@@ -4605,10 +4610,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4631,19 +4636,19 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>79</v>
@@ -4692,7 +4697,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4707,27 +4712,27 @@
         <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4753,13 +4758,13 @@
         <v>262</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4785,11 +4790,11 @@
         <v>79</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>79</v>
@@ -4807,7 +4812,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4822,16 +4827,16 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>79</v>
@@ -4839,10 +4844,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4865,16 +4870,16 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4924,7 +4929,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -4939,27 +4944,27 @@
         <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4982,13 +4987,13 @@
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5039,7 +5044,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5054,10 +5059,10 @@
         <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>79</v>
@@ -5071,14 +5076,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5097,16 +5102,16 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5156,7 +5161,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5174,10 +5179,10 @@
         <v>79</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>79</v>
@@ -5188,10 +5193,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5214,13 +5219,13 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5271,7 +5276,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5289,7 +5294,7 @@
         <v>79</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>79</v>
@@ -5303,10 +5308,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5329,13 +5334,13 @@
         <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5386,7 +5391,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5404,7 +5409,7 @@
         <v>79</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>79</v>
@@ -5418,10 +5423,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5450,7 +5455,7 @@
         <v>137</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N32" t="s" s="2">
         <v>139</v>
@@ -5503,7 +5508,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5521,7 +5526,7 @@
         <v>79</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>79</v>
@@ -5535,14 +5540,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5564,10 +5569,10 @@
         <v>136</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>139</v>
@@ -5622,7 +5627,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5654,14 +5659,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5683,16 +5688,16 @@
         <v>92</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>79</v>
@@ -5705,7 +5710,7 @@
         <v>79</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="U34" t="s" s="2">
         <v>79</v>
@@ -5741,7 +5746,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>90</v>
@@ -5759,10 +5764,10 @@
         <v>79</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>79</v>
@@ -5773,14 +5778,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5802,10 +5807,10 @@
         <v>241</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5820,7 +5825,7 @@
         <v>79</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="U35" t="s" s="2">
         <v>79</v>
@@ -5856,7 +5861,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5874,10 +5879,10 @@
         <v>79</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>79</v>
@@ -5888,14 +5893,14 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5917,13 +5922,13 @@
         <v>171</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5971,7 +5976,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>90</v>
@@ -5992,7 +5997,7 @@
         <v>176</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>79</v>
@@ -6003,14 +6008,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6029,13 +6034,13 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6050,7 +6055,7 @@
         <v>79</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>79</v>
@@ -6086,7 +6091,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6104,10 +6109,10 @@
         <v>79</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>79</v>
@@ -6118,14 +6123,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6147,10 +6152,10 @@
         <v>241</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6201,7 +6206,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6222,7 +6227,7 @@
         <v>250</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>79</v>
@@ -6233,10 +6238,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6262,16 +6267,16 @@
         <v>233</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>79</v>
@@ -6320,7 +6325,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6352,14 +6357,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6381,10 +6386,10 @@
         <v>171</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>265</v>
@@ -6413,13 +6418,13 @@
         <v>79</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>79</v>
@@ -6437,7 +6442,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6455,10 +6460,10 @@
         <v>79</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>79</v>
@@ -6469,10 +6474,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6498,10 +6503,10 @@
         <v>171</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N41" t="s" s="2">
         <v>265</v>
@@ -6530,13 +6535,13 @@
         <v>79</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>79</v>
@@ -6554,7 +6559,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6572,10 +6577,10 @@
         <v>79</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>79</v>
@@ -6586,10 +6591,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6612,13 +6617,13 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>265</v>
@@ -6671,7 +6676,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6689,10 +6694,10 @@
         <v>79</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>79</v>
@@ -6703,10 +6708,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6732,13 +6737,13 @@
         <v>198</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6788,7 +6793,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6809,7 +6814,7 @@
         <v>203</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>79</v>
@@ -6820,14 +6825,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6846,19 +6851,19 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N44" t="s" s="2">
         <v>265</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -6907,7 +6912,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -6922,13 +6927,13 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>229</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>79</v>
@@ -6939,10 +6944,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6965,13 +6970,13 @@
         <v>79</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7022,7 +7027,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7040,7 +7045,7 @@
         <v>79</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>79</v>
@@ -7054,10 +7059,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7086,7 +7091,7 @@
         <v>137</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>139</v>
@@ -7139,7 +7144,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7157,7 +7162,7 @@
         <v>79</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>79</v>
@@ -7171,14 +7176,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7200,10 +7205,10 @@
         <v>136</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>139</v>
@@ -7258,7 +7263,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7290,10 +7295,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7319,16 +7324,16 @@
         <v>262</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>265</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -7356,10 +7361,10 @@
         <v>266</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>79</v>
@@ -7377,7 +7382,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7409,10 +7414,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7435,13 +7440,13 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>265</v>
@@ -7494,7 +7499,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>90</v>
@@ -7512,24 +7517,24 @@
         <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7552,13 +7557,13 @@
         <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7609,7 +7614,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7627,7 +7632,7 @@
         <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>79</v>
@@ -7641,10 +7646,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7667,13 +7672,13 @@
         <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7724,7 +7729,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7742,7 +7747,7 @@
         <v>79</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>79</v>
@@ -7756,10 +7761,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7788,7 +7793,7 @@
         <v>137</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>139</v>
@@ -7841,7 +7846,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -7859,7 +7864,7 @@
         <v>79</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>79</v>
@@ -7873,14 +7878,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7902,10 +7907,10 @@
         <v>136</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>139</v>
@@ -7960,7 +7965,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -7992,14 +7997,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8021,16 +8026,16 @@
         <v>92</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>79</v>
@@ -8043,7 +8048,7 @@
         <v>79</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>79</v>
@@ -8079,7 +8084,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>90</v>
@@ -8097,10 +8102,10 @@
         <v>79</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>79</v>
@@ -8111,14 +8116,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8140,13 +8145,13 @@
         <v>171</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8175,10 +8180,10 @@
         <v>266</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>79</v>
@@ -8196,7 +8201,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>90</v>
@@ -8214,10 +8219,10 @@
         <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>79</v>
@@ -8228,14 +8233,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8257,13 +8262,13 @@
         <v>241</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8313,7 +8318,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8331,10 +8336,10 @@
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>79</v>
@@ -8345,10 +8350,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8371,16 +8376,16 @@
         <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8430,7 +8435,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8448,10 +8453,10 @@
         <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>79</v>
